--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,46 +1127,53 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24791</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>148</v>
       </c>
       <c r="K12" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2025</v>
+        <v>20242025</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1175,60 +1182,852 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>laliga</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45527.6875</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>148</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>148</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>148</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>148</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>148</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>148</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45665.66666666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>real madrid</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>mallorca</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>148</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="J26" t="n">
+        <v>148</v>
+      </c>
+      <c r="K26" t="n">
         <v>1484</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M26" t="n">
         <v>2025</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,53 +1251,46 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23516</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>148</v>
       </c>
       <c r="K14" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1306,53 +1299,53 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>super cup</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>148</v>
       </c>
       <c r="K15" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1360,674 +1353,6 @@
         </is>
       </c>
       <c r="O15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>148</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>148</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>valladolid</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>148</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.58333333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>12454</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>leganes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>148</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45529.59375</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>148</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45529.6875</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>148</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45530.6875</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>148</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45531.58333333334</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>148</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45531.6875</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>148</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>148</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1484</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>148</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1484</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,46 +1251,53 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.5</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>148</v>
       </c>
       <c r="K14" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2025</v>
+        <v>20242025</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1299,60 +1306,480 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>laliga</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>148</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>real madrid</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>148</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>mallorca</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>148</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J22" t="n">
+        <v>148</v>
+      </c>
+      <c r="K22" t="n">
         <v>1484</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M22" t="n">
         <v>2025</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2302,116 +2302,6 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>148</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1484</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>148</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1484</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,266 +507,1444 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>148</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>148</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>148</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>148</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>148</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>148</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>148</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>148</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>148</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio el sadar
   pamplona </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E21" t="n">
         <v>23516</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>ETdxjU8a</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>osasuna</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>148</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>55926</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>148</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lopez m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>148</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>148</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">coliseum
   getafe </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E23" t="n">
         <v>16500</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>dboeiWOt</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>getafe</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>148</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>148</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45536.6875</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>148</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23000</v>
+        <v>53331</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26020</v>
+        <v>27618</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
+          <t xml:space="preserve">metropolitano stadium
   madrid </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14505</v>
+        <v>70460</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,313 +708,303 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>148</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>148</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio san mames
   bilbao </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>53331</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>IP5zl0cJ</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ath bilbao</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>148</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45532.58333333334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>valladolid</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>leganes</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>148</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45532.6875</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>148</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45532.6875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>148</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45533.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maeso f 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14624</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>osasuna</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1043,45 +1033,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45533.6875</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
+        <v>45535.59375</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1110,40 +1095,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>55926</v>
+        <v>12454</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1172,40 +1157,40 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53331</v>
+        <v>49430</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1234,40 +1219,40 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>40000</v>
+        <v>19840</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1296,40 +1281,40 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12454</v>
+        <v>23516</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1358,40 +1343,40 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49430</v>
+        <v>42714</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1420,40 +1405,40 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.59375</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19840</v>
+        <v>16500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1482,40 +1467,40 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.6875</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>23516</v>
+        <v>83186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1536,192 +1521,6 @@
         </is>
       </c>
       <c r="O17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>148</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>148</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>148</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53331</v>
+        <v>55926</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27618</v>
+        <v>53331</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.59375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70460</v>
+        <v>40000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>12454</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14624</v>
+        <v>49430</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,45 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32392</v>
+        <v>19840</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>IyRQC2vM</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>las palmas</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>real madrid</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -909,40 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45536.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55926</v>
+        <v>23516</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,40 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53331</v>
+        <v>42714</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1033,40 +1043,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.59375</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45536.59375</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40000</v>
+        <v>16500</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1095,40 +1110,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.6875</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>45536.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12454</v>
+        <v>83186</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1149,378 +1169,6 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45535.6875</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>148</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>148</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>148</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>148</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>148</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>148</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55926</v>
+        <v>19840</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53331</v>
+        <v>23516</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40000</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.59375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12454</v>
+        <v>16500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49430</v>
+        <v>83186</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -834,341 +834,6 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>148</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>148</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>148</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>148</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>148</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
+        <v>45548.66666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19840</v>
+        <v>60721</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23516</v>
+        <v>26020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.46875</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42714</v>
+        <v>40000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.5625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16500</v>
+        <v>42714</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>dboeiWOt</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>getafe</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>83186</v>
+        <v>40000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>betis</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -834,6 +809,316 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>148</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,998 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45552.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>148</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>148</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>148</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>148</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>148</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>148</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>148</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>148</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>148</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,395 +507,1935 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.375</v>
+        <v>45552.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>148</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>148</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>148</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>148</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>148</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>148</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>148</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>148</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45560.58333333334</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>148</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de balaidos
   vigo </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E22" t="n">
         <v>24791</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>8pvUZFhf</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>celta vigo</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>148</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>valladolid</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>148</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.46875</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>14624</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>148</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>148</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>148</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>148</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>148</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>nNNpcUSL</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>girona</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>148</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>32392</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J28" t="n">
+        <v>148</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>IP5zl0cJ</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>ath bilbao</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>148</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>148</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>148</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45564.66666666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">metropolitano stadium
   madrid </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E31" t="n">
         <v>70460</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>atl  madrid</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>148</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45551.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>148</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45552.58333333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>148</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>148</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>148</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,395 +507,1801 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.375</v>
+        <v>45558.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>148</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>148</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>148</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>148</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45560.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>148</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>148</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de balaidos
   vigo </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E10" t="n">
         <v>24791</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>8pvUZFhf</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>celta vigo</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>valladolid</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>148</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.46875</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>148</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>148</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>148</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45569.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45570.375</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>148</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45570.46875</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>148</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>148</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>148</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>148</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio municipal de montilivi
   girona </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E27" t="n">
         <v>14624</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>nNNpcUSL</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>girona</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>148</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>barcelona</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>148</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>32392</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>148</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="J28" t="n">
+        <v>148</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45571.5625</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>148</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45571.66666666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>atl  madrid</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>148</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45551.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>148</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45552.58333333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>148</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="J30" t="n">
+        <v>148</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27618</v>
+        <v>24791</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.375</v>
+        <v>45564.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16500</v>
+        <v>53331</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45564.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14505</v>
+        <v>60721</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.5625</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>70460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23516</v>
+        <v>23000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -834,274 +834,6 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>148</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.46875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>148</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>60721</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>148</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.66666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>148</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.375</v>
+        <v>45569.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24791</v>
+        <v>12454</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.46875</v>
+        <v>45570.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53331</v>
+        <v>40000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5625</v>
+        <v>45570.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60721</v>
+        <v>16500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70460</v>
+        <v>32392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23000</v>
+        <v>27618</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -834,6 +834,527 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>148</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>148</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.46875</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.66666666666</v>
+        <v>45571.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12454</v>
+        <v>14624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.375</v>
+        <v>45571.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40000</v>
+        <v>19840</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.46875</v>
+        <v>45571.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16500</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45571.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27618</v>
+        <v>19840</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>valladolid</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,45 +837,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>83186</v>
+        <v>53331</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -909,45 +899,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.46875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14624</v>
+        <v>23516</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -976,45 +961,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.46875</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19840</v>
+        <v>14624</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1043,45 +1023,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.5625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>42714</v>
+        <v>24791</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1110,45 +1085,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.66666666666</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
+        <v>45585.375</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40000</v>
+        <v>26020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1177,40 +1147,40 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45585.46875</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19840</v>
+        <v>70460</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1239,40 +1209,40 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.375</v>
+        <v>45585.5625</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53331</v>
+        <v>23000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1301,40 +1271,40 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23516</v>
+        <v>55926</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="J14" t="n">

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45583.66666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio mendizorrotza
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45584.375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio san mames
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45584.46875</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio el sadar
@@ -699,7 +714,12 @@
       <c r="B5" s="2" t="n">
         <v>45584.5625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio municipal de montilivi
@@ -761,7 +781,12 @@
       <c r="B6" s="2" t="n">
         <v>45584.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de balaidos
@@ -823,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45585.375</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi mallorca son moix
@@ -885,7 +915,12 @@
       <c r="B8" s="2" t="n">
         <v>45585.46875</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">metropolitano stadium
@@ -947,7 +982,12 @@
       <c r="B9" s="2" t="n">
         <v>45585.5625</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de la ceramica
@@ -1009,7 +1049,12 @@
       <c r="B10" s="2" t="n">
         <v>45585.66666666666</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi olimpic lluis companys
@@ -1071,7 +1116,12 @@
       <c r="B11" s="2" t="n">
         <v>45586.66666666666</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de mestalla

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,333 +507,1238 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
+        <v>45590.66666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>148</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>148</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.46875</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>14708</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>148</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>148</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>148</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.51041666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>148</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.60416666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>148</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.70833333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45593.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi mallorca son moix
   palma de mallorca </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E11" t="n">
         <v>26020</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>mallorca</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>148</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.51041666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>8bcjFy6O</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>rayo vallecano</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>148</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.46875</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>148</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">metropolitano stadium
   madrid </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E17" t="n">
         <v>70460</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>atl  madrid</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>leganes</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>148</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45585.5625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>148</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45585.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.51041666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi olimpic lluis companys
   barcelona </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E18" t="n">
         <v>55926</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>barcelona</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>148</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>h8oAv4Ts</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>sevilla</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>148</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45586.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>148</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45599.70833333334</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45590.66666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">rcde stadium
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45591.375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio jose zorrilla
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45591.46875</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">campo de futbol de vallecas
@@ -699,7 +714,12 @@
       <c r="B5" s="2" t="n">
         <v>45591.5625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de gran canaria
@@ -761,7 +781,12 @@
       <c r="B6" s="2" t="n">
         <v>45591.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio santiago bernabeu
@@ -823,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45592.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio municipal de butarque
@@ -885,7 +915,12 @@
       <c r="B8" s="2" t="n">
         <v>45592.51041666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">coliseum
@@ -947,7 +982,12 @@
       <c r="B9" s="2" t="n">
         <v>45592.60416666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio benito villamarin
@@ -1009,7 +1049,12 @@
       <c r="B10" s="2" t="n">
         <v>45592.70833333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">reale arena
@@ -1071,7 +1116,12 @@
       <c r="B11" s="2" t="n">
         <v>45593.70833333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi mallorca son moix
@@ -1119,626 +1169,6 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>148</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>valladolid</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>148</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.51041666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>14624</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>leganes</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>148</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>148</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>148</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>148</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.51041666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>55926</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>148</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>148</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45599.70833333334</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>148</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>148</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,40 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45599.41666666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23000</v>
+        <v>70460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45599.51041666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49430</v>
+        <v>55926</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +817,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.41666666666</v>
+        <v>45599.60416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70460</v>
+        <v>42714</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +879,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.51041666666</v>
+        <v>45599.70833333334</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55926</v>
+        <v>53331</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +941,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.60416666666</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42714</v>
+        <v>24791</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -995,750 +995,6 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45599.70833333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>148</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>148</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45604.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>14708</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>148</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>148</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.51041666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>148</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>148</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>148</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>60721</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>148</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.51041666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>148</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>12454</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>leganes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>148</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>valladolid</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>148</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45606.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>148</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,40 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45604.70833333334</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19840</v>
+        <v>14708</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -569,40 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.41666666666</v>
+        <v>45605.41666666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23516</v>
+        <v>83186</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>ETdxjU8a</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>osasuna</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>valladolid</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.51041666666</v>
+        <v>45605.51041666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14624</v>
+        <v>23000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.41666666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70460</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.51041666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55926</v>
+        <v>12454</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +817,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.60416666666</v>
+        <v>45606.41666666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
+          <t xml:space="preserve">estadio benito villamarin
   sevilla </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42714</v>
+        <v>60721</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +879,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.70833333334</v>
+        <v>45606.51041666666</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53331</v>
+        <v>26020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +941,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.60416666666</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24791</v>
+        <v>16500</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -995,6 +995,130 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/spain/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45604.70833333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">campo de futbol de vallecas
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45605.41666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio santiago bernabeu
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45605.51041666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de la ceramica
@@ -693,40 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>12454</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45606.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12454</v>
+        <v>60721</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45606.51041666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60721</v>
+        <v>26020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45606.51041666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26020</v>
+        <v>16500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>45606.60416666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16500</v>
+        <v>27618</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1003,40 +1043,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27618</v>
+        <v>40000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1065,40 +1110,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.70833333334</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40000</v>
+        <v>16500</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1119,6 +1164,254 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>148</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.51041666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>148</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>148</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
